--- a/zy70670/test_statistics.xlsx
+++ b/zy70670/test_statistics.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
